--- a/outputs/tables/tabla_sobredispersion.xlsx
+++ b/outputs/tables/tabla_sobredispersion.xlsx
@@ -7,14 +7,15 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Cameron-Trivedi" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Parámetro</t>
   </si>
@@ -46,7 +47,28 @@
     <t>Justificación</t>
   </si>
   <si>
-    <t>Existe evidencia estadística robusta de SOBREDISPERSIÓN en la distribución espacial de los homicidios (Varianza = 569.41 &gt;&gt; Media = 18.99, con un ratio de 29.98). El test formal de Cameron &amp; Trivedi rechaza la hipótesis nula de equidispersión de Poisson de forma significativa (alpha = 1.5195, t = 3.92, p-valor = 1.134467e-04). Esto justifica plenamente descartar el modelo frecuentista Poisson clásico y adoptar un modelo con estructura Binomial Negativa que incorpore efectos aleatorios espaciales y temporales bajo un enfoque Bayesiano Jerárquico.</t>
+    <t>Existe evidencia estadística robusta de SOBREDISPERSIÓN en la distribución espacial de los homicidios (Varianza = 527.31 &gt;&gt; Media = 18.16, con un ratio de 29.03). El test formal de Cameron &amp; Trivedi rechaza la hipótesis nula de equidispersión de Poisson de forma significativa (alpha = 1.5367, t = 3.85, p-valor = 1.539366e-04). Esto justifica plenamente descartar el modelo frecuentista Poisson clásico y adoptar un modelo con estructura Binomial Negativa que incorpore efectos aleatorios espaciales y temporales bajo un enfoque Bayesiano Jerárquico.</t>
+  </si>
+  <si>
+    <t>Parámetro del Test</t>
+  </si>
+  <si>
+    <t>Estimación</t>
+  </si>
+  <si>
+    <t>Parámetro de Sobredispersión (alpha)</t>
+  </si>
+  <si>
+    <t>Estadístico t</t>
+  </si>
+  <si>
+    <t>p-valor (Cameron &amp; Trivedi 1990)</t>
+  </si>
+  <si>
+    <t>Decisión Metodológica</t>
+  </si>
+  <si>
+    <t>Rechazo de H0 de Poisson (Sobredispersión Significativa)</t>
   </si>
 </sst>
 </file>
@@ -420,7 +442,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>18.99180327868853</v>
+        <v>18.16393442622951</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -428,7 +450,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>569.4073399446805</v>
+        <v>527.3145786952709</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -436,7 +458,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>29.98174168029824</v>
+        <v>29.03085676932448</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -444,7 +466,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1.519543208526643</v>
+        <v>1.536664755177314</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -452,7 +474,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3.923935957169607</v>
+        <v>3.845144357568792</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -460,7 +482,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.0001134467099422043</v>
+        <v>0.000153936572653418</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -477,6 +499,56 @@
       </c>
       <c r="B9" t="s">
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>1.5367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>3.8451</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>0.000154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
